--- a/excel/Viainvest.xlsx
+++ b/excel/Viainvest.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Viainvest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Viainvest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4C544E-6C14-4C26-825D-B55E0083850D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC360DC-CE16-4A98-BD9C-54FA0FC4E56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="LVX0000V2GD7" sheetId="37" r:id="rId3"/>
-    <sheet name="LVX0000USE62" sheetId="36" r:id="rId4"/>
-    <sheet name="LVX0000UNB86" sheetId="35" r:id="rId5"/>
-    <sheet name="LVX0000U8E70" sheetId="34" r:id="rId6"/>
-    <sheet name="LVX0000TWW26" sheetId="33" r:id="rId7"/>
-    <sheet name="LVX0000TKSY9" sheetId="32" r:id="rId8"/>
-    <sheet name="LVX0000TK694" sheetId="31" r:id="rId9"/>
-    <sheet name="LVX0000T5YE5" sheetId="30" r:id="rId10"/>
-    <sheet name="LVX0000SFML1" sheetId="29" r:id="rId11"/>
-    <sheet name="LVX0000RLIY2" sheetId="28" r:id="rId12"/>
-    <sheet name="LVX0000QU0F1" sheetId="27" r:id="rId13"/>
-    <sheet name="LVX0000PXSI3" sheetId="26" r:id="rId14"/>
-    <sheet name="LVX0000PK205" sheetId="25" r:id="rId15"/>
-    <sheet name="LVX0000PRFL6" sheetId="14" r:id="rId16"/>
+    <sheet name="LVX0000V9912" sheetId="38" r:id="rId3"/>
+    <sheet name="LVX0000V2GD7" sheetId="37" r:id="rId4"/>
+    <sheet name="LVX0000USE62" sheetId="36" r:id="rId5"/>
+    <sheet name="LVX0000UNB86" sheetId="35" r:id="rId6"/>
+    <sheet name="LVX0000U8E70" sheetId="34" r:id="rId7"/>
+    <sheet name="LVX0000TWW26" sheetId="33" r:id="rId8"/>
+    <sheet name="LVX0000TKSY9" sheetId="32" r:id="rId9"/>
+    <sheet name="LVX0000TK694" sheetId="31" r:id="rId10"/>
+    <sheet name="LVX0000T5YE5" sheetId="30" r:id="rId11"/>
+    <sheet name="LVX0000SFML1" sheetId="29" r:id="rId12"/>
+    <sheet name="LVX0000RLIY2" sheetId="28" r:id="rId13"/>
+    <sheet name="LVX0000QU0F1" sheetId="27" r:id="rId14"/>
+    <sheet name="LVX0000PXSI3" sheetId="26" r:id="rId15"/>
+    <sheet name="LVX0000PK205" sheetId="25" r:id="rId16"/>
+    <sheet name="LVX0000PRFL6" sheetId="14" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="62">
   <si>
     <t>Paskola</t>
   </si>
@@ -227,9 +228,6 @@
     <t>LVX0000V2GD7</t>
   </si>
   <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
     <t>Komapanija</t>
   </si>
   <si>
@@ -237,6 +235,9 @@
   </si>
   <si>
     <t>Eur.</t>
+  </si>
+  <si>
+    <t>LVX0000V9912</t>
   </si>
 </sst>
 </file>
@@ -380,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -447,40 +448,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -493,12 +463,61 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="64">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -953,7 +972,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC6D9C7-B788-445B-BB13-B0B2B397B38A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE5C62C-4C2E-4BFE-877B-B6A5C2A3DF27}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1009,7 +1028,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1065,7 +1084,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1121,7 +1140,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1177,6 +1196,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD13F6DB-3617-4E16-85C6-CE67C2928B61}"/>
             </a:ext>
           </a:extLst>
@@ -1212,7 +1287,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1289,7 +1364,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92ED2B6F-42A8-45C2-AF4C-D0E530F0061A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC6D9C7-B788-445B-BB13-B0B2B397B38A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1345,7 +1420,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92ED2B6F-42A8-45C2-AF4C-D0E530F0061A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1401,7 +1476,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1457,7 +1532,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1513,7 +1588,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1569,7 +1644,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1625,7 +1700,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1681,7 +1756,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1997,44 +2072,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="27" t="s">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="29"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="33"/>
       <c r="M1" s="34" t="s">
         <v>25</v>
       </c>
       <c r="N1" s="34"/>
       <c r="O1" s="34"/>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="30" t="s">
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="27" t="s">
+      <c r="V1" s="37"/>
+      <c r="W1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="26" t="s">
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2051,8 +2126,8 @@
       <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="26" t="s">
-        <v>59</v>
+      <c r="E2" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>21</v>
@@ -2075,26 +2150,26 @@
       <c r="L2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" s="26" t="s">
+      <c r="M2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="O2" s="4" t="s">
         <v>38</v>
       </c>
       <c r="P2" s="8"/>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="R2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="T2" s="26" t="s">
+      <c r="S2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="U2" s="22" t="s">
@@ -2103,20 +2178,20 @@
       <c r="V2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="W2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2" s="26" t="s">
+      <c r="X2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="26" t="s">
+      <c r="Z2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="26" t="s">
-        <v>61</v>
+      <c r="AA2" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AC2" s="11" t="s">
         <v>41</v>
@@ -2183,49 +2258,49 @@
         <v>8.9999999999999983E-2</v>
       </c>
       <c r="P3" s="9"/>
-      <c r="Q3" s="38">
+      <c r="Q3" s="27">
         <f>Pinigai!I2</f>
-        <v>340</v>
-      </c>
-      <c r="R3" s="39">
+        <v>360</v>
+      </c>
+      <c r="R3" s="28">
         <f>SUM(H3:H100)-U3</f>
-        <v>348.46999999999997</v>
-      </c>
-      <c r="S3" s="38">
+        <v>364.11999999999995</v>
+      </c>
+      <c r="S3" s="27">
         <f>Pinigai!H2</f>
         <v>0</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="27">
         <f>W3-R3</f>
-        <v>9.8800000000000523</v>
-      </c>
-      <c r="U3" s="39">
+        <v>14.60000000000008</v>
+      </c>
+      <c r="U3" s="28">
         <f>SUM(M3:M100)</f>
-        <v>432.33</v>
-      </c>
-      <c r="V3" s="39">
+        <v>469.45</v>
+      </c>
+      <c r="V3" s="28">
         <f>SUM(N3:N100)-AA3</f>
-        <v>18.349999999999998</v>
-      </c>
-      <c r="W3" s="38">
+        <v>18.72</v>
+      </c>
+      <c r="W3" s="27">
         <f>Q3+S3+V3</f>
-        <v>358.35</v>
-      </c>
-      <c r="X3" s="38">
+        <v>378.72</v>
+      </c>
+      <c r="X3" s="27">
         <f>W3-Q3</f>
-        <v>18.350000000000023</v>
-      </c>
-      <c r="Y3" s="40">
+        <v>18.720000000000027</v>
+      </c>
+      <c r="Y3" s="29">
         <f>(W3-Q3)/Q3</f>
-        <v>5.3970588235294187E-2</v>
-      </c>
-      <c r="Z3" s="41">
+        <v>5.2000000000000074E-2</v>
+      </c>
+      <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>9.2625096440315274E-2</v>
-      </c>
-      <c r="AA3" s="38">
+        <v>8.9276906847953821E-2</v>
+      </c>
+      <c r="AA3" s="27">
         <f>SUM(O3:O100)</f>
-        <v>0.94000000000000017</v>
+        <v>0.96000000000000019</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">LVX0000PRFL6!Z3</f>
@@ -2293,17 +2368,16 @@
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="P4" s="9"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="37"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
       <c r="AC4" s="3" t="str">
         <f ca="1">LVX0000PK205!Z3</f>
         <v/>
@@ -2549,7 +2623,7 @@
       </c>
       <c r="K8" s="18">
         <f ca="1">LVX0000SFML1!B12</f>
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L8" s="18" t="str">
         <f ca="1">LVX0000SFML1!P3</f>
@@ -2681,7 +2755,7 @@
       </c>
       <c r="K10" s="18">
         <f ca="1">LVX0000TK694!B12</f>
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="L10" s="18" t="str">
         <f ca="1">LVX0000TK694!P3</f>
@@ -2689,7 +2763,7 @@
       </c>
       <c r="M10" s="3">
         <f>LVX0000TK694!K3</f>
-        <v>7.69</v>
+        <v>30.21</v>
       </c>
       <c r="N10" s="3">
         <f>LVX0000TK694!L3</f>
@@ -2747,7 +2821,7 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">LVX0000TKSY9!B12</f>
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">LVX0000TKSY9!P3</f>
@@ -2755,7 +2829,7 @@
       </c>
       <c r="M11" s="3">
         <f>LVX0000TKSY9!K3</f>
-        <v>22.7</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="N11" s="3">
         <f>LVX0000TKSY9!L3</f>
@@ -2813,7 +2887,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">LVX0000TWW26!B12</f>
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">LVX0000TWW26!P3</f>
@@ -2825,11 +2899,11 @@
       </c>
       <c r="N12" s="3">
         <f>LVX0000TWW26!L3</f>
-        <v>0.88</v>
+        <v>1.27</v>
       </c>
       <c r="O12" s="3">
         <f>LVX0000TWW26!M3</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AC12" s="3" t="str">
         <f ca="1">LVX0000TWW26!Z3</f>
@@ -2878,7 +2952,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">LVX0000U8E70!B12</f>
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">LVX0000U8E70!P3</f>
@@ -2943,7 +3017,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">LVX0000UNB86!B12</f>
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">LVX0000UNB86!P3</f>
@@ -3008,7 +3082,7 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">LVX0000USE62!B12</f>
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="L15" s="18" t="str">
         <f ca="1">LVX0000USE62!P3</f>
@@ -3073,7 +3147,7 @@
       </c>
       <c r="K16" s="18">
         <f ca="1">LVX0000V2GD7!B12</f>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="L16" s="18" t="str">
         <f ca="1">LVX0000V2GD7!P3</f>
@@ -3097,22 +3171,69 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="AC17" s="1"/>
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6">
+        <f>LVX0000V9912!B9</f>
+        <v>46238</v>
+      </c>
+      <c r="C17" s="24" t="str">
+        <f>LVX0000V9912!B1</f>
+        <v>LVX0000V9912</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f>LVX0000V9912!B2</f>
+        <v>Latvia</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>LVX0000V9912!B3</f>
+        <v>SIA VIA SMS (LV)</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f>LVX0000V9912!B8</f>
+        <v>0 m. 8 mėn. 22 d.</v>
+      </c>
+      <c r="G17" s="7">
+        <f>LVX0000V9912!B15</f>
+        <v>0.11</v>
+      </c>
+      <c r="H17" s="3">
+        <f>LVX0000V9912!B16</f>
+        <v>52.77</v>
+      </c>
+      <c r="I17" s="6">
+        <f>LVX0000V9912!B11</f>
+        <v>46503</v>
+      </c>
+      <c r="J17" s="6" t="str">
+        <f>LVX0000V9912!O3</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
+        <f ca="1">LVX0000V9912!B12</f>
+        <v>262</v>
+      </c>
+      <c r="L17" s="18" t="str">
+        <f ca="1">LVX0000V9912!P3</f>
+        <v/>
+      </c>
+      <c r="M17" s="3">
+        <f>LVX0000V9912!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <f>LVX0000V9912!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <f>LVX0000V9912!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="str">
+        <f ca="1">LVX0000V9912!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
@@ -3296,28 +3417,28 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="W1:Z1"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
-    <cfRule type="expression" dxfId="59" priority="7">
+    <cfRule type="expression" dxfId="63" priority="9">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="11">
+    <cfRule type="expression" dxfId="62" priority="13">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="61" priority="2">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC16">
-    <cfRule type="expression" dxfId="56" priority="1">
+  <conditionalFormatting sqref="AC6:AC17">
+    <cfRule type="expression" dxfId="60" priority="1">
       <formula>$AC6="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3335,7 +3456,8 @@
     <hyperlink ref="C13" location="LVX0000U8E70!A1" display="LVX0000U8E70!A1" xr:uid="{D41A3630-A56F-4916-B1AA-C5C3695F19A8}"/>
     <hyperlink ref="C14" location="LVX0000UNB86!A1" display="LVX0000UNB86!A1" xr:uid="{8B58AC79-8F19-4849-BA55-1D38985B2EEB}"/>
     <hyperlink ref="C15" location="LVX0000USE62!A1" display="LVX0000USE62!A1" xr:uid="{F1C40DAB-27D9-44D4-8895-8D55B6EA57EA}"/>
-    <hyperlink ref="C16" location="LVX0000USE62!A1" display="LVX0000USE62!A1" xr:uid="{7D5E87E6-238B-4A7E-89F7-EBB2FDF1E71C}"/>
+    <hyperlink ref="C16" location="LVX0000V2GD7!A1" display="LVX0000V2GD7!A1" xr:uid="{7D5E87E6-238B-4A7E-89F7-EBB2FDF1E71C}"/>
+    <hyperlink ref="C17" location="LVX0000V9912!A1" display="LVX0000V9912!A1" xr:uid="{24F01A4B-53A5-479B-B485-7512C7E50621}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3343,6 +3465,1340 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46156</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46156</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>30.21</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0.06</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46126</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-54.23</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46160</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46160</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6.15</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46156</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10">
+        <v>46187</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46187</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.45</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46160</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10">
+        <v>46191</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46191</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46187</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10">
+        <v>46217</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46217</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46191</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 5 mėn. 29 d.</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46237</v>
+      </c>
+      <c r="E8" s="10">
+        <v>46237</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>22.52</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46217</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0.39999999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46126</v>
+      </c>
+      <c r="D9" s="10">
+        <v>46248</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46237</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>22.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46126</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46308</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>67</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>54.23</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>30.21</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0.06</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="31" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="29" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="28" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3372,29 +4828,29 @@
       <c r="B1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4666,7 +6122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4693,29 +6149,29 @@
       <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5055,7 +6511,9 @@
       <c r="B10" s="6">
         <v>46068</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>46250</v>
+      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="18" t="str">
         <f t="shared" si="0"/>
@@ -5106,7 +6564,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -6008,7 +7466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D1CAB2-9974-4180-AFF6-5274525FE544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6038,29 +7496,29 @@
       <c r="B1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7373,7 +8831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3754DA4B-78B4-44BD-BB4B-39C6D453FDD0}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -7403,29 +8861,29 @@
       <c r="B1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8738,7 +10196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A46497B-E391-4B8F-8947-28547C504629}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8768,29 +10226,29 @@
       <c r="B1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10097,7 +11555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE44972-B3BE-4780-9CE5-89011043CB83}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10127,29 +11585,29 @@
       <c r="B1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11456,7 +12914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -11486,29 +12944,29 @@
       <c r="B1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -12895,7 +14353,7 @@
       </c>
       <c r="F2" s="3">
         <f>SUM(B2:B35)</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="G2" s="3">
         <f>SUM(C2:C35)</f>
@@ -12907,7 +14365,7 @@
       </c>
       <c r="I2" s="3">
         <f>F2-G2</f>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="K2" s="3">
         <f>B2*-1</f>
@@ -13077,13 +14535,21 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="6">
+        <v>46237</v>
+      </c>
+      <c r="B12" s="3">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
       <c r="K12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -14407,14 +15873,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46229</v>
+        <v>46241</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="25">
         <f>Overview!W3</f>
-        <v>358.35</v>
+        <v>378.72</v>
       </c>
     </row>
   </sheetData>
@@ -14423,6 +15889,1280 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD327B7-A614-4292-902F-A1D77443615E}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46268</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="18" t="str">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46238</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-52.77</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 8 mėn. 22 d.</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46238</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46237</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46503</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>262</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>52.77</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="59" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="57" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="56" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9162ACA-AF34-4907-9FD0-1619591C6350}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14449,29 +17189,29 @@
       <c r="B1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14537,7 +17277,9 @@
       <c r="B3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="10">
+        <v>46246</v>
+      </c>
       <c r="E3" s="10"/>
       <c r="F3" s="18" t="str">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
@@ -14792,7 +17534,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -15694,7 +18436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636E6C87-D2E9-45C3-AA9C-63A3C4369065}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15721,29 +18463,29 @@
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15878,7 +18620,9 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>46255</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="18" t="str">
         <f t="shared" si="0"/>
@@ -16074,7 +18818,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -16976,7 +19720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA74071-CEE0-4172-8957-6D5916CFD11C}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17003,29 +19747,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -17192,7 +19936,9 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="10">
+        <v>46246</v>
+      </c>
       <c r="E5" s="10"/>
       <c r="F5" s="18" t="str">
         <f t="shared" si="0"/>
@@ -17366,7 +20112,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -18268,7 +21014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39A4C94-8C03-41D4-B944-5DB24FED2BD0}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18295,29 +21041,29 @@
       <c r="B1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18484,8 +21230,8 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10" t="s">
-        <v>58</v>
+      <c r="D5" s="10">
+        <v>46222</v>
       </c>
       <c r="E5" s="10">
         <v>46222</v>
@@ -18516,7 +21262,9 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="10">
+        <v>46253</v>
+      </c>
       <c r="E6" s="10"/>
       <c r="F6" s="18" t="str">
         <f t="shared" si="0"/>
@@ -18668,7 +21416,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -19570,7 +22318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51596B63-3E30-4F0D-ACA7-3B11B25E71A9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19597,29 +22345,29 @@
       <c r="B1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -19711,11 +22459,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.88</v>
+        <v>1.27</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -19850,15 +22598,25 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="D7" s="10">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46236</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -19877,7 +22635,9 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>0 m. 5 mėn. 29 d.</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="10">
+        <v>46267</v>
+      </c>
       <c r="E8" s="10"/>
       <c r="F8" s="18" t="str">
         <f t="shared" si="0"/>
@@ -19889,11 +22649,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46236</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -19980,7 +22740,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -20844,11 +23604,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.88</v>
+        <v>1.27</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -20882,7 +23642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20909,29 +23669,29 @@
       <c r="B1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
       <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -21019,7 +23779,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>22.7</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
@@ -21162,15 +23922,25 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="D7" s="10">
+        <v>46242</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46242</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
@@ -21189,7 +23959,9 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>0 m. 5 mėn. 29 d.</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="10">
+        <v>46249</v>
+      </c>
       <c r="E8" s="10"/>
       <c r="F8" s="18" t="str">
         <f t="shared" si="0"/>
@@ -21201,11 +23973,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46242</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -21292,7 +24064,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -22152,7 +24924,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>22.7</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
@@ -22192,1326 +24964,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="29"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="29"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="10">
-        <v>46156</v>
-      </c>
-      <c r="E3" s="10">
-        <v>46156</v>
-      </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>7.69</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0.06</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46126</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-54.23</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46160</v>
-      </c>
-      <c r="E4" s="10">
-        <v>46160</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>6.15</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46156</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="10">
-        <v>46187</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46187</v>
-      </c>
-      <c r="F5" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.45</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46160</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="10">
-        <v>46191</v>
-      </c>
-      <c r="E6" s="10">
-        <v>46191</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1.54</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46187</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="10">
-        <v>46217</v>
-      </c>
-      <c r="E7" s="10">
-        <v>46217</v>
-      </c>
-      <c r="F7" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.42</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46191</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 5 mėn. 29 d.</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46217</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0.39999999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46126</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="13"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46126</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="13"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46308</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="13"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="18">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>79</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="13"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="13"/>
-      <c r="N13" s="15"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="13"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3">
-        <v>54.23</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="13"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="13"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="13"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="13"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="13"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="13"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="13"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="13"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="13"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="13"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="13"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="13"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="13"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="13"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="13"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>7.69</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0.06</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="31" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="29" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="28" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/excel/Viainvest.xlsx
+++ b/excel/Viainvest.xlsx
@@ -5,31 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Viainvest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Viainvest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC360DC-CE16-4A98-BD9C-54FA0FC4E56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1953713-3D21-4350-9487-3D285BDBF15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="LVX0000V9912" sheetId="38" r:id="rId3"/>
-    <sheet name="LVX0000V2GD7" sheetId="37" r:id="rId4"/>
-    <sheet name="LVX0000USE62" sheetId="36" r:id="rId5"/>
-    <sheet name="LVX0000UNB86" sheetId="35" r:id="rId6"/>
-    <sheet name="LVX0000U8E70" sheetId="34" r:id="rId7"/>
-    <sheet name="LVX0000TWW26" sheetId="33" r:id="rId8"/>
-    <sheet name="LVX0000TKSY9" sheetId="32" r:id="rId9"/>
-    <sheet name="LVX0000TK694" sheetId="31" r:id="rId10"/>
-    <sheet name="LVX0000T5YE5" sheetId="30" r:id="rId11"/>
-    <sheet name="LVX0000SFML1" sheetId="29" r:id="rId12"/>
-    <sheet name="LVX0000RLIY2" sheetId="28" r:id="rId13"/>
-    <sheet name="LVX0000QU0F1" sheetId="27" r:id="rId14"/>
-    <sheet name="LVX0000PXSI3" sheetId="26" r:id="rId15"/>
-    <sheet name="LVX0000PK205" sheetId="25" r:id="rId16"/>
-    <sheet name="LVX0000PRFL6" sheetId="14" r:id="rId17"/>
+    <sheet name="LVX0000VDAW2" sheetId="39" r:id="rId3"/>
+    <sheet name="LVX0000V9912" sheetId="38" r:id="rId4"/>
+    <sheet name="LVX0000V2GD7" sheetId="37" r:id="rId5"/>
+    <sheet name="LVX0000USE62" sheetId="36" r:id="rId6"/>
+    <sheet name="LVX0000UNB86" sheetId="35" r:id="rId7"/>
+    <sheet name="LVX0000U8E70" sheetId="34" r:id="rId8"/>
+    <sheet name="LVX0000TWW26" sheetId="33" r:id="rId9"/>
+    <sheet name="LVX0000TKSY9" sheetId="32" r:id="rId10"/>
+    <sheet name="LVX0000TK694" sheetId="31" r:id="rId11"/>
+    <sheet name="LVX0000T5YE5" sheetId="30" r:id="rId12"/>
+    <sheet name="LVX0000SFML1" sheetId="29" r:id="rId13"/>
+    <sheet name="LVX0000RLIY2" sheetId="28" r:id="rId14"/>
+    <sheet name="LVX0000QU0F1" sheetId="27" r:id="rId15"/>
+    <sheet name="LVX0000PXSI3" sheetId="26" r:id="rId16"/>
+    <sheet name="LVX0000PK205" sheetId="25" r:id="rId17"/>
+    <sheet name="LVX0000PRFL6" sheetId="14" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="63">
   <si>
     <t>Paskola</t>
   </si>
@@ -238,6 +239,9 @@
   </si>
   <si>
     <t>LVX0000V9912</t>
+  </si>
+  <si>
+    <t>LVX0000VDAW2</t>
   </si>
 </sst>
 </file>
@@ -489,7 +493,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="68">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -972,7 +1004,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE5C62C-4C2E-4BFE-877B-B6A5C2A3DF27}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABCCDA00-1D44-42BF-B0C9-18F6831F98EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1028,7 +1060,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1084,7 +1116,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB14DA99-6B92-49A0-A498-AA9896FB5940}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,7 +1172,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78E2DBBC-C5B2-4288-AC0A-95368A14A86A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1196,7 +1228,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B495DA4-2D50-43E7-92C9-52E679196A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1252,6 +1284,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D9ED54-8C5F-4763-A103-EA86015ECDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD13F6DB-3617-4E16-85C6-CE67C2928B61}"/>
             </a:ext>
           </a:extLst>
@@ -1287,7 +1375,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1364,7 +1452,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC6D9C7-B788-445B-BB13-B0B2B397B38A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FE5C62C-4C2E-4BFE-877B-B6A5C2A3DF27}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1420,7 +1508,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92ED2B6F-42A8-45C2-AF4C-D0E530F0061A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC6D9C7-B788-445B-BB13-B0B2B397B38A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1476,7 +1564,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92ED2B6F-42A8-45C2-AF4C-D0E530F0061A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1532,7 +1620,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D26DB4C-231C-4C87-87A9-E78886E7807B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1588,7 +1676,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13F58B75-E6DB-4D82-A45E-AB511FF3C881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1644,7 +1732,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75ADCD55-EE0C-46E9-9BA6-6DDCE4741191}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1700,7 +1788,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4516F9B9-44DD-4606-BEE5-CB1D2AAA0AF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1756,7 +1844,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D2C6C96-E314-400B-9CB5-8B0597A3C6F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2810C3BC-F093-4506-BBA0-6D497E73A3C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2068,7 +2156,7 @@
     <col min="11" max="12" width="8.7109375" customWidth="1"/>
     <col min="13" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="25" width="10.7109375" customWidth="1"/>
+    <col min="17" max="27" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -2264,7 +2352,7 @@
       </c>
       <c r="R3" s="28">
         <f>SUM(H3:H100)-U3</f>
-        <v>364.11999999999995</v>
+        <v>377.93999999999994</v>
       </c>
       <c r="S3" s="27">
         <f>Pinigai!H2</f>
@@ -2272,35 +2360,35 @@
       </c>
       <c r="T3" s="27">
         <f>W3-R3</f>
-        <v>14.60000000000008</v>
+        <v>3.3100000000000591</v>
       </c>
       <c r="U3" s="28">
         <f>SUM(M3:M100)</f>
-        <v>469.45</v>
+        <v>506.79999999999995</v>
       </c>
       <c r="V3" s="28">
         <f>SUM(N3:N100)-AA3</f>
-        <v>18.72</v>
+        <v>21.249999999999996</v>
       </c>
       <c r="W3" s="27">
         <f>Q3+S3+V3</f>
-        <v>378.72</v>
+        <v>381.25</v>
       </c>
       <c r="X3" s="27">
         <f>W3-Q3</f>
-        <v>18.720000000000027</v>
+        <v>21.25</v>
       </c>
       <c r="Y3" s="29">
         <f>(W3-Q3)/Q3</f>
-        <v>5.2000000000000074E-2</v>
+        <v>5.9027777777777776E-2</v>
       </c>
       <c r="Z3" s="30">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>8.9276906847953821E-2</v>
+        <v>9.058896601200106E-2</v>
       </c>
       <c r="AA3" s="27">
         <f>SUM(O3:O100)</f>
-        <v>0.96000000000000019</v>
+        <v>1.1100000000000003</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">LVX0000PRFL6!Z3</f>
@@ -2617,13 +2705,13 @@
         <f>LVX0000SFML1!B11</f>
         <v>46250</v>
       </c>
-      <c r="J8" s="6" t="str">
+      <c r="J8" s="6">
         <f>LVX0000SFML1!O3</f>
-        <v/>
-      </c>
-      <c r="K8" s="18">
+        <v>46252</v>
+      </c>
+      <c r="K8" s="18" t="str">
         <f ca="1">LVX0000SFML1!B12</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="L8" s="18" t="str">
         <f ca="1">LVX0000SFML1!P3</f>
@@ -2631,15 +2719,15 @@
       </c>
       <c r="M8" s="3">
         <f>LVX0000SFML1!K3</f>
-        <v>16.66</v>
+        <v>51.510000000000005</v>
       </c>
       <c r="N8" s="3">
         <f>LVX0000SFML1!L3</f>
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="O8" s="3">
         <f>LVX0000SFML1!M3</f>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="P8" s="9"/>
       <c r="AC8" s="3" t="str">
@@ -2755,7 +2843,7 @@
       </c>
       <c r="K10" s="18">
         <f ca="1">LVX0000TK694!B12</f>
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L10" s="18" t="str">
         <f ca="1">LVX0000TK694!P3</f>
@@ -2767,11 +2855,11 @@
       </c>
       <c r="N10" s="3">
         <f>LVX0000TK694!L3</f>
-        <v>1.3599999999999999</v>
+        <v>1.7199999999999998</v>
       </c>
       <c r="O10" s="3">
         <f>LVX0000TK694!M3</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="P10" s="9"/>
       <c r="AC10" s="3" t="str">
@@ -2821,7 +2909,7 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">LVX0000TKSY9!B12</f>
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L11" s="18" t="str">
         <f ca="1">LVX0000TKSY9!P3</f>
@@ -2833,11 +2921,11 @@
       </c>
       <c r="N11" s="3">
         <f>LVX0000TKSY9!L3</f>
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="O11" s="3">
         <f>LVX0000TKSY9!M3</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="P11" s="9"/>
       <c r="AC11" s="3" t="str">
@@ -2887,7 +2975,7 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">LVX0000TWW26!B12</f>
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="L12" s="18" t="str">
         <f ca="1">LVX0000TWW26!P3</f>
@@ -2952,7 +3040,7 @@
       </c>
       <c r="K13" s="18">
         <f ca="1">LVX0000U8E70!B12</f>
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="L13" s="18" t="str">
         <f ca="1">LVX0000U8E70!P3</f>
@@ -2960,15 +3048,15 @@
       </c>
       <c r="M13" s="3">
         <f>LVX0000U8E70!K3</f>
-        <v>14.9</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="N13" s="3">
         <f>LVX0000U8E70!L3</f>
-        <v>0.79</v>
+        <v>1.1300000000000001</v>
       </c>
       <c r="O13" s="3">
         <f>LVX0000U8E70!M3</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AC13" s="3" t="str">
         <f ca="1">LVX0000U8E70!Z3</f>
@@ -3017,7 +3105,7 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">LVX0000UNB86!B12</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L14" s="18" t="str">
         <f ca="1">LVX0000UNB86!P3</f>
@@ -3029,11 +3117,11 @@
       </c>
       <c r="N14" s="3">
         <f>LVX0000UNB86!L3</f>
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="O14" s="3">
         <f>LVX0000UNB86!M3</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="AC14" s="3" t="str">
         <f ca="1">LVX0000UNB86!Z3</f>
@@ -3082,7 +3170,7 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">LVX0000USE62!B12</f>
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="L15" s="18" t="str">
         <f ca="1">LVX0000USE62!P3</f>
@@ -3094,11 +3182,11 @@
       </c>
       <c r="N15" s="3">
         <f>LVX0000USE62!L3</f>
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="O15" s="3">
         <f>LVX0000USE62!M3</f>
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AC15" s="3" t="str">
         <f ca="1">LVX0000USE62!Z3</f>
@@ -3147,7 +3235,7 @@
       </c>
       <c r="K16" s="18">
         <f ca="1">LVX0000V2GD7!B12</f>
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="L16" s="18" t="str">
         <f ca="1">LVX0000V2GD7!P3</f>
@@ -3159,11 +3247,11 @@
       </c>
       <c r="N16" s="3">
         <f>LVX0000V2GD7!L3</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O16" s="3">
         <f>LVX0000V2GD7!M3</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AC16" s="3" t="str">
         <f ca="1">LVX0000V2GD7!Z3</f>
@@ -3212,7 +3300,7 @@
       </c>
       <c r="K17" s="18">
         <f ca="1">LVX0000V9912!B12</f>
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="L17" s="18" t="str">
         <f ca="1">LVX0000V9912!P3</f>
@@ -3236,22 +3324,69 @@
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="AC18" s="1"/>
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6">
+        <f>LVX0000VDAW2!B9</f>
+        <v>46252</v>
+      </c>
+      <c r="C18" s="24" t="str">
+        <f>LVX0000VDAW2!B1</f>
+        <v>LVX0000VDAW2</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f>LVX0000VDAW2!B2</f>
+        <v>Latvia</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>LVX0000VDAW2!B3</f>
+        <v>SIA VIA SMS (LV)</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f>LVX0000VDAW2!B8</f>
+        <v>0 m. 8 mėn. 20 d.</v>
+      </c>
+      <c r="G18" s="7">
+        <f>LVX0000VDAW2!B15</f>
+        <v>0.11</v>
+      </c>
+      <c r="H18" s="3">
+        <f>LVX0000VDAW2!B16</f>
+        <v>51.17</v>
+      </c>
+      <c r="I18" s="6">
+        <f>LVX0000VDAW2!B11</f>
+        <v>46515</v>
+      </c>
+      <c r="J18" s="6" t="str">
+        <f>LVX0000VDAW2!O3</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f ca="1">LVX0000VDAW2!B12</f>
+        <v>249</v>
+      </c>
+      <c r="L18" s="18" t="str">
+        <f ca="1">LVX0000VDAW2!P3</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
+        <f>LVX0000VDAW2!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <f>LVX0000VDAW2!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <f>LVX0000VDAW2!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3" t="str">
+        <f ca="1">LVX0000VDAW2!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
@@ -3425,20 +3560,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
-    <cfRule type="expression" dxfId="63" priority="9">
+    <cfRule type="expression" dxfId="67" priority="9">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="13">
+    <cfRule type="expression" dxfId="66" priority="13">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="61" priority="2">
+    <cfRule type="expression" dxfId="65" priority="2">
       <formula>AND($H3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC17">
-    <cfRule type="expression" dxfId="60" priority="1">
+  <conditionalFormatting sqref="AC6:AC18">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>$AC6="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3458,6 +3593,7 @@
     <hyperlink ref="C15" location="LVX0000USE62!A1" display="LVX0000USE62!A1" xr:uid="{F1C40DAB-27D9-44D4-8895-8D55B6EA57EA}"/>
     <hyperlink ref="C16" location="LVX0000V2GD7!A1" display="LVX0000V2GD7!A1" xr:uid="{7D5E87E6-238B-4A7E-89F7-EBB2FDF1E71C}"/>
     <hyperlink ref="C17" location="LVX0000V9912!A1" display="LVX0000V9912!A1" xr:uid="{24F01A4B-53A5-479B-B485-7512C7E50621}"/>
+    <hyperlink ref="C18" location="LVX0000VDAW2!A1" display="LVX0000VDAW2!A1" xr:uid="{587BD9D2-B648-4836-8AC1-48D7FBC46EEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3465,6 +3601,1340 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46157</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46157</v>
+      </c>
+      <c r="F3" s="18">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>37.299999999999997</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>1.19</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0.05</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46127</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-50.44</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46161</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46161</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>22.7</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46157</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10">
+        <v>46188</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46188</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46161</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10">
+        <v>46218</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46218</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46188</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10">
+        <v>46242</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46242</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46218</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 5 mėn. 29 d.</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46249</v>
+      </c>
+      <c r="E8" s="10">
+        <v>46249</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46242</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46127</v>
+      </c>
+      <c r="D9" s="10">
+        <v>46280</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46249</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46127</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46309</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>43</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>50.44</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>37.299999999999997</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>1.19</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="35" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="33" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="32" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B83440-5743-4944-A92C-7C00476AA6BD}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3605,11 +5075,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.3599999999999999</v>
+        <v>1.7199999999999998</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -3820,14 +5290,22 @@
       <c r="D9" s="10">
         <v>46248</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="E9" s="10">
+        <v>46248</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J9" s="13"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
@@ -3845,7 +5323,9 @@
       <c r="B10" s="6">
         <v>46126</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>46279</v>
+      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3857,11 +5337,11 @@
       <c r="J10" s="13"/>
       <c r="X10" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46248</v>
       </c>
       <c r="Y10" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.33999999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -3896,7 +5376,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -4760,11 +6240,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.3599999999999999</v>
+        <v>1.7199999999999998</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -4798,7 +6278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8F9EBE-D214-44A2-8A19-768E491F391C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6122,8 +7602,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E465F013-9FF2-44FD-828F-D999C3230D4E}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6259,31 +7742,31 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>16.66</v>
+        <v>51.510000000000005</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.1</v>
-      </c>
-      <c r="N3" s="7" t="str">
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.10715524554252626</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46252</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="T3" s="15"/>
       <c r="X3" s="6">
@@ -6512,16 +7995,24 @@
         <v>46068</v>
       </c>
       <c r="D10" s="10">
-        <v>46250</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+        <v>46249</v>
+      </c>
+      <c r="E10" s="10">
+        <v>46249</v>
+      </c>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J10" s="13"/>
       <c r="X10" s="6">
         <f t="shared" si="1"/>
@@ -6539,32 +8030,42 @@
       <c r="B11" s="6">
         <v>46250</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
+      <c r="D11" s="10">
+        <v>46250</v>
+      </c>
+      <c r="E11" s="10">
+        <v>46252</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G11" s="3">
+        <v>34.85</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
       <c r="J11" s="13"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46249</v>
       </c>
       <c r="Y11" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="18" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -6578,11 +8079,11 @@
       <c r="J12" s="13"/>
       <c r="X12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46252</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -7424,15 +8925,15 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>16.66</v>
+        <v>51.510000000000005</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +8967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D1CAB2-9974-4180-AFF6-5274525FE544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8831,7 +10332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3754DA4B-78B4-44BD-BB4B-39C6D453FDD0}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10196,7 +11697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A46497B-E391-4B8F-8947-28547C504629}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -11555,7 +13056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE44972-B3BE-4780-9CE5-89011043CB83}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -12914,7 +14415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -15873,14 +17374,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46241</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="25">
         <f>Overview!W3</f>
-        <v>378.72</v>
+        <v>381.25</v>
       </c>
     </row>
   </sheetData>
@@ -15889,6 +17390,1280 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B40014-6D8E-459C-B8AC-E9C506ECE65D}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="33"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="33"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46282</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="18" t="str">
+        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="15"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46252</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-51.17</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="13"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 8 mėn. 20 d.</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46252</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="13"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="13"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46515</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="13"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>249</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="13"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="13"/>
+      <c r="N13" s="15"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="19"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="13"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>51.17</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="13"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="13"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="13"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="13"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="13"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="13"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="13"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="13"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="13"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="13"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="13"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="13"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="13"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="13"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="13"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="13"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="13"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="13"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="13"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="13"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="13"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="13"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="13"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="13"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="13"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="13"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="13"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="13"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="13"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="13"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="13"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="13"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="13"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="13"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="13"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="63" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="61" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="60" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD327B7-A614-4292-902F-A1D77443615E}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16260,7 +19035,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -17162,7 +19937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9162ACA-AF34-4907-9FD0-1619591C6350}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17280,14 +20055,22 @@
       <c r="D3" s="10">
         <v>46246</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="18" t="str">
+      <c r="E3" s="10">
+        <v>46246</v>
+      </c>
+      <c r="F3" s="18">
         <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.03</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -17295,11 +20078,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -17338,7 +20121,9 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>46277</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="18" t="str">
         <f t="shared" si="0"/>
@@ -17350,11 +20135,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46246</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -17534,7 +20319,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -18398,11 +21183,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -18436,7 +21221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636E6C87-D2E9-45C3-AA9C-63A3C4369065}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18577,11 +21362,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -18623,14 +21408,22 @@
       <c r="D4" s="10">
         <v>46255</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="E4" s="10">
+        <v>46255</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.03</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -18656,11 +21449,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46255</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -18818,7 +21611,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -19682,11 +22475,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -19720,7 +22513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA74071-CEE0-4172-8957-6D5916CFD11C}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19861,11 +22654,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -19939,14 +22732,22 @@
       <c r="D5" s="10">
         <v>46246</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="E5" s="10">
+        <v>46246</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -19960,7 +22761,9 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="10">
+        <v>46277</v>
+      </c>
       <c r="E6" s="10"/>
       <c r="F6" s="18" t="str">
         <f t="shared" si="0"/>
@@ -19972,11 +22775,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46246</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.38999999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -20112,7 +22915,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -20976,11 +23779,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -21014,7 +23817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39A4C94-8C03-41D4-B944-5DB24FED2BD0}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21151,15 +23954,15 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>14.9</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.79</v>
+        <v>1.1300000000000001</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -21265,14 +24068,22 @@
       <c r="D6" s="10">
         <v>46253</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="E6" s="10">
+        <v>46253</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -21286,23 +24097,33 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="D7" s="10">
+        <v>46256</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46256</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
       <c r="J7" s="13"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46253</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -21313,7 +24134,9 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>0 m. 5 mėn. 29 d.</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="10">
+        <v>46284</v>
+      </c>
       <c r="E8" s="10"/>
       <c r="F8" s="18" t="str">
         <f t="shared" si="0"/>
@@ -21325,11 +24148,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46256</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -21416,7 +24239,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -22276,15 +25099,15 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>14.9</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.79</v>
+        <v>1.1300000000000001</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -22318,7 +25141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51596B63-3E30-4F0D-ACA7-3B11B25E71A9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22740,7 +25563,7 @@
       </c>
       <c r="B12" s="18">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -23640,1328 +26463,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6787A89-4537-4E64-91BF-0AA0F96019C3}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="13" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="33"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="33"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="10">
-        <v>46157</v>
-      </c>
-      <c r="E3" s="10">
-        <v>46157</v>
-      </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F52" si="0">IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.46</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>37.299999999999997</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.97</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0.04</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="15"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46127</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-50.44</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46161</v>
-      </c>
-      <c r="E4" s="10">
-        <v>46161</v>
-      </c>
-      <c r="F4" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>22.7</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46157</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="10">
-        <v>46188</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46188</v>
-      </c>
-      <c r="F5" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.26</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46161</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="10">
-        <v>46218</v>
-      </c>
-      <c r="E6" s="10">
-        <v>46218</v>
-      </c>
-      <c r="F6" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46188</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="10">
-        <v>46242</v>
-      </c>
-      <c r="E7" s="10">
-        <v>46242</v>
-      </c>
-      <c r="F7" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>14.6</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46218</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 5 mėn. 29 d.</v>
-      </c>
-      <c r="D8" s="10">
-        <v>46249</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46242</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46127</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="13"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46127</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="13"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46309</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="13"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="18">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>68</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="13"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="13"/>
-      <c r="N13" s="15"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="13"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3">
-        <v>50.44</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="13"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="13"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="13"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="13"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="13"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="13"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="13"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="13"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="13"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="13"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="13"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="13"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="13"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="13"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="13"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="13"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="13"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="13"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="13"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="13"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="13"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="13"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="13"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="13"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="13"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="13"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="13"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="13"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="13"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="13"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="13"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="13"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="13"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="13"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="13"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>37.299999999999997</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.97</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0.04</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="35" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="33" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="32" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>